--- a/docs/assets/3rdparty/source/icecream-flavours-altLabels.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours-altLabels.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t>Banana</t>
   </si>
@@ -191,205 +191,205 @@
     <t>FLAVOR NAMES</t>
   </si>
   <si>
-    <t>icf:45b0a9d3-d3c9-4c19-b4ef-0511a8827101</t>
-  </si>
-  <si>
-    <t>icf:abf359ff-5c42-42e1-91a5-21973879f6f0</t>
-  </si>
-  <si>
-    <t>icf:0f748e6f-ae0b-49a9-bac9-98db1de6fd04</t>
-  </si>
-  <si>
-    <t>icf:bf94fff7-9ef5-4af6-91dc-bf332e1bbd72</t>
-  </si>
-  <si>
-    <t>icf:556b0f61-f107-4519-8bbe-cf3c29d840bb</t>
-  </si>
-  <si>
-    <t>icf:79aaa965-5e88-4a01-8b5a-87438ff46cf6</t>
-  </si>
-  <si>
-    <t>icf:4343af06-9db2-43d4-920a-61d349ef42f5</t>
-  </si>
-  <si>
-    <t>icf:f476202a-b952-4b55-8877-33570ee26cf5</t>
-  </si>
-  <si>
-    <t>icf:cd2071b4-cb2e-4c12-ad82-fa7b2c844899</t>
-  </si>
-  <si>
-    <t>icf:61ed4c66-f7d8-40c9-8866-cc4bdee3ea44</t>
-  </si>
-  <si>
-    <t>icf:9e8afe4c-f6db-40e3-a625-7dbeadc1a3d5</t>
-  </si>
-  <si>
-    <t>icf:a5120bb8-2a39-4b7e-95e4-c05646ab53e2</t>
-  </si>
-  <si>
-    <t>icf:7b276e8c-ac83-4eb0-8b8d-e26f0f00d190</t>
-  </si>
-  <si>
-    <t>icf:ccb7b867-4f44-4eea-bd09-99f964664733</t>
-  </si>
-  <si>
-    <t>icf:b8af11ac-39c5-4547-8ff0-1cb77e50f9d5</t>
-  </si>
-  <si>
-    <t>icf:bd9289fa-9715-4a2e-89bd-bc4f705dc167</t>
-  </si>
-  <si>
-    <t>icf:0e9b17d8-339c-4a55-8157-03b15be56f76</t>
-  </si>
-  <si>
-    <t>icf:d35b1641-f112-4ab5-83fe-95e98229f4e7</t>
-  </si>
-  <si>
-    <t>icf:a1a144fd-3f41-4961-9bb1-47ac783232b5</t>
-  </si>
-  <si>
-    <t>icf:9de1e781-4733-4cbe-8cb2-143d7a4ed92f</t>
-  </si>
-  <si>
-    <t>icf:e702da60-1dbe-48ee-891f-e1de99ee07d5</t>
-  </si>
-  <si>
-    <t>icf:2f524245-e21c-4c02-966d-f3b4022535ea</t>
-  </si>
-  <si>
-    <t>icf:c4c2344c-4b1b-462a-b9f9-e1b03faeb0dd</t>
-  </si>
-  <si>
-    <t>icf:f4fe093d-96d6-4419-8079-1fdba8a479cc</t>
-  </si>
-  <si>
-    <t>icf:66dcdd54-fffb-4d29-90bc-0be9a9d052b5</t>
-  </si>
-  <si>
-    <t>icf:a61185c1-786a-4a93-8964-0d53686baddd</t>
-  </si>
-  <si>
-    <t>icf:aa64a8c2-8dbb-428b-94f9-fc328870d3ec</t>
-  </si>
-  <si>
-    <t>icf:2307a8fb-e802-403a-b255-6ec1a57677aa</t>
-  </si>
-  <si>
-    <t>icf:e8555003-5203-47d4-af04-70798add66ad</t>
-  </si>
-  <si>
-    <t>icf:f7bbc944-ecdc-4517-8f71-6ac6653db5c4</t>
-  </si>
-  <si>
-    <t>icf:678299ea-ae67-4736-b109-02f3b5c2e752</t>
-  </si>
-  <si>
-    <t>icf:cd7ecf43-79b3-4495-98a5-fea33b86a29c</t>
-  </si>
-  <si>
-    <t>icf:10cdc74f-c236-42cf-bb32-33f40c882189</t>
-  </si>
-  <si>
-    <t>icf:1619cc1c-c75b-45d1-bdaf-ced29978673f</t>
-  </si>
-  <si>
-    <t>icf:bbe41b1a-5eb1-4d35-af25-673b0c0c842d</t>
-  </si>
-  <si>
-    <t>icf:98656441-5fd4-42e8-bd11-cfce8fae4a86</t>
-  </si>
-  <si>
-    <t>icf:6148a62f-1ae4-4797-9f6a-359f17c2c60a</t>
-  </si>
-  <si>
-    <t>icf:f8892819-70b5-4efc-8e42-43d1024d943e</t>
-  </si>
-  <si>
-    <t>icf:d4ef5ab1-2fd4-4b70-b7a0-ad79605f5e4e</t>
-  </si>
-  <si>
-    <t>icf:5c2bad30-3036-4394-abef-1daf0cb6351d</t>
-  </si>
-  <si>
-    <t>icf:07ff3c57-c075-4a95-be6a-99955621dd5c</t>
-  </si>
-  <si>
-    <t>icf:3c71c026-00b2-435e-bb8b-66d006e7b133</t>
-  </si>
-  <si>
-    <t>icf:ade1b5f0-58c6-46a8-8faa-6ed4224c72b7</t>
-  </si>
-  <si>
-    <t>icf:23798250-a926-42ba-95ce-c5576efa0bec</t>
-  </si>
-  <si>
-    <t>icf:a886dea1-e597-40a2-84c2-f91f1750c724</t>
-  </si>
-  <si>
-    <t>icf:06f52b88-9ad0-4214-bf41-f5c23514d2cd</t>
-  </si>
-  <si>
-    <t>icf:28d8e6bb-6003-451e-b21e-292b4c5067f4</t>
-  </si>
-  <si>
-    <t>icf:48493fe1-dccb-45d0-9082-90ee9cb2e2f6</t>
-  </si>
-  <si>
-    <t>icf:cf5e8785-f0d9-4d8f-bcd8-c196b3751051</t>
-  </si>
-  <si>
-    <t>icf:a91c45b3-4168-4326-ba6f-6300858fde67</t>
-  </si>
-  <si>
-    <t>icf:a06e660a-7ca5-4213-88a9-5c2ea3574899</t>
-  </si>
-  <si>
-    <t>icf:8f32f706-4827-4b52-8658-97af4cfa0398</t>
-  </si>
-  <si>
-    <t>icf:295b3fc1-a889-4960-bdbd-304392d1f0ec</t>
-  </si>
-  <si>
-    <t>icf:033da6cd-a916-467c-bbea-a6cd7b2fd9a3</t>
-  </si>
-  <si>
-    <t>icf:f8463b04-fa44-41b7-bb42-acc83a089cbb</t>
-  </si>
-  <si>
-    <t>icf:cc6b3ba1-b7ef-4ea9-b60a-77c52c1bb74d</t>
-  </si>
-  <si>
-    <t>icf:e54eea7d-074b-4d7b-8d73-d0df22b1f3e3</t>
-  </si>
-  <si>
-    <t>icf:2db0fe98-c26f-4cde-955e-53e0cbe5ee8e</t>
-  </si>
-  <si>
-    <t>icf:abb0e61b-5c54-4984-a13b-780563887653</t>
-  </si>
-  <si>
-    <t>icf:f550c468-b125-49ff-a3f2-1876954f7f73</t>
-  </si>
-  <si>
-    <t>icf:1671e56f-52db-48af-a0a5-e45f8eb66053</t>
-  </si>
-  <si>
-    <t>icf:88947dcc-ef36-4bda-b26f-d91b9bbb92d9</t>
-  </si>
-  <si>
-    <t>icf:b868d0d7-e574-48b0-a6b2-433a01c7434a</t>
-  </si>
-  <si>
-    <t>icf:b023c80a-7d05-4324-8207-4e5bba5dec17</t>
-  </si>
-  <si>
-    <t>icf:96e04174-022b-4934-a431-3bb3f96f015f</t>
-  </si>
-  <si>
-    <t>icf:392def8f-2e32-4c23-ae4f-2f149787f3a6</t>
-  </si>
-  <si>
-    <t>icf:8e63e629-3b8f-47d7-86d8-079bc74dc92c</t>
+    <t>icf:2</t>
+  </si>
+  <si>
+    <t>icf:3</t>
+  </si>
+  <si>
+    <t>icf:4</t>
+  </si>
+  <si>
+    <t>icf:5</t>
+  </si>
+  <si>
+    <t>icf:6</t>
+  </si>
+  <si>
+    <t>icf:7</t>
+  </si>
+  <si>
+    <t>icf:8</t>
+  </si>
+  <si>
+    <t>icf:9</t>
+  </si>
+  <si>
+    <t>icf:10</t>
+  </si>
+  <si>
+    <t>icf:11</t>
+  </si>
+  <si>
+    <t>icf:12</t>
+  </si>
+  <si>
+    <t>icf:13</t>
+  </si>
+  <si>
+    <t>icf:14</t>
+  </si>
+  <si>
+    <t>icf:15</t>
+  </si>
+  <si>
+    <t>icf:16</t>
+  </si>
+  <si>
+    <t>icf:17</t>
+  </si>
+  <si>
+    <t>icf:18</t>
+  </si>
+  <si>
+    <t>icf:19</t>
+  </si>
+  <si>
+    <t>icf:20</t>
+  </si>
+  <si>
+    <t>icf:21</t>
+  </si>
+  <si>
+    <t>icf:23</t>
+  </si>
+  <si>
+    <t>icf:24</t>
+  </si>
+  <si>
+    <t>icf:25</t>
+  </si>
+  <si>
+    <t>icf:26</t>
+  </si>
+  <si>
+    <t>icf:27</t>
+  </si>
+  <si>
+    <t>icf:28</t>
+  </si>
+  <si>
+    <t>icf:29</t>
+  </si>
+  <si>
+    <t>icf:30</t>
+  </si>
+  <si>
+    <t>icf:31</t>
+  </si>
+  <si>
+    <t>icf:32</t>
+  </si>
+  <si>
+    <t>icf:33</t>
+  </si>
+  <si>
+    <t>icf:34</t>
+  </si>
+  <si>
+    <t>icf:35</t>
+  </si>
+  <si>
+    <t>icf:36</t>
+  </si>
+  <si>
+    <t>icf:37</t>
+  </si>
+  <si>
+    <t>icf:38</t>
+  </si>
+  <si>
+    <t>icf:39</t>
+  </si>
+  <si>
+    <t>icf:40</t>
+  </si>
+  <si>
+    <t>icf:41</t>
+  </si>
+  <si>
+    <t>icf:42</t>
+  </si>
+  <si>
+    <t>icf:43</t>
+  </si>
+  <si>
+    <t>icf:44</t>
+  </si>
+  <si>
+    <t>icf:45</t>
+  </si>
+  <si>
+    <t>icf:46</t>
+  </si>
+  <si>
+    <t>icf:47</t>
+  </si>
+  <si>
+    <t>icf:48</t>
+  </si>
+  <si>
+    <t>icf:49</t>
+  </si>
+  <si>
+    <t>icf:50</t>
+  </si>
+  <si>
+    <t>icf:51</t>
+  </si>
+  <si>
+    <t>icf:52</t>
+  </si>
+  <si>
+    <t>icf:53</t>
+  </si>
+  <si>
+    <t>icf:54</t>
+  </si>
+  <si>
+    <t>icf:55</t>
+  </si>
+  <si>
+    <t>icf:56</t>
+  </si>
+  <si>
+    <t>icf:57</t>
+  </si>
+  <si>
+    <t>icf:59</t>
+  </si>
+  <si>
+    <t>icf:60</t>
+  </si>
+  <si>
+    <t>icf:61</t>
+  </si>
+  <si>
+    <t>icf:62</t>
+  </si>
+  <si>
+    <t>icf:63</t>
+  </si>
+  <si>
+    <t>icf:64</t>
+  </si>
+  <si>
+    <t>icf:65</t>
+  </si>
+  <si>
+    <t>icf:66</t>
+  </si>
+  <si>
+    <t>icf:67</t>
+  </si>
+  <si>
+    <t>icf:68</t>
+  </si>
+  <si>
+    <t>icf:69</t>
+  </si>
+  <si>
+    <t>icf:70</t>
   </si>
   <si>
     <t xml:space="preserve">Cherry </t>
@@ -528,6 +528,18 @@
   </si>
   <si>
     <t>purple yam</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>icf:1</t>
+  </si>
+  <si>
+    <t>icf:22</t>
+  </si>
+  <si>
+    <t>icf:58</t>
   </si>
 </sst>
 </file>
@@ -913,9 +925,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
   <dimension ref="A1:D74"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
     <col min="2" max="2" width="35.1640625" customWidth="1"/>
@@ -923,7 +935,10 @@
     <col min="4" max="4" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>163</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
@@ -934,17 +949,21 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>164</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -953,7 +972,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -962,7 +981,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -976,7 +995,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -985,7 +1004,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -994,7 +1013,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1005,7 +1024,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1014,7 +1033,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ns3:dyDescent="0.2">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1023,7 +1042,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -1034,7 +1053,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -1043,7 +1062,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1052,7 +1071,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -1063,7 +1082,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1072,7 +1091,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -1081,7 +1100,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ns3:dyDescent="0.2">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1090,7 +1109,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1099,7 +1118,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1108,7 +1127,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -1119,7 +1138,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -1128,7 +1147,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -1137,17 +1156,21 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A24"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>165</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -1158,7 +1181,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>71</v>
       </c>
@@ -1169,7 +1192,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -1178,7 +1201,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>73</v>
       </c>
@@ -1189,7 +1212,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1198,7 +1221,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>75</v>
       </c>
@@ -1209,7 +1232,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1218,7 +1241,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -1227,7 +1250,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1236,7 +1259,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1247,7 +1270,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>80</v>
       </c>
@@ -1256,7 +1279,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -1265,7 +1288,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -1274,7 +1297,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>83</v>
       </c>
@@ -1283,7 +1306,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>84</v>
       </c>
@@ -1292,7 +1315,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -1301,7 +1324,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -1310,7 +1333,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1319,7 +1342,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -1330,7 +1353,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -1339,7 +1362,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1348,7 +1371,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ns3:dyDescent="0.2">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -1359,7 +1382,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -1368,7 +1391,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>93</v>
       </c>
@@ -1379,7 +1402,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -1388,7 +1411,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -1399,7 +1422,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -1408,7 +1431,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -1417,7 +1440,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -1428,7 +1451,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>99</v>
       </c>
@@ -1437,7 +1460,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -1448,7 +1471,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -1457,7 +1480,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -1466,7 +1489,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>103</v>
       </c>
@@ -1477,7 +1500,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -1486,17 +1509,21 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A61"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ns3:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>166</v>
+      </c>
       <c r="B62" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -1507,7 +1534,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>106</v>
       </c>
@@ -1516,7 +1543,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>107</v>
       </c>
@@ -1525,7 +1552,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>108</v>
       </c>
@@ -1534,7 +1561,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>109</v>
       </c>
@@ -1545,7 +1572,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>110</v>
       </c>
@@ -1554,7 +1581,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>111</v>
       </c>
@@ -1563,7 +1590,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -1572,7 +1599,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>113</v>
       </c>
@@ -1581,7 +1608,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>114</v>
       </c>
@@ -1590,7 +1617,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>115</v>
       </c>
@@ -1601,10 +1628,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>116</v>
-      </c>
+    <row r="74" spans="1:4" ns3:dyDescent="0.2">
+      <c r="A74"/>
       <c r="B74" s="2" t="s">
         <v>161</v>
       </c>
